--- a/data/age/raw/Age Batch Detail June 2026.xlsx
+++ b/data/age/raw/Age Batch Detail June 2026.xlsx
@@ -8,31 +8,45 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\00_GitHub\Atnarko-sockeye\data\age\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CAC66BC-4D5E-4E31-AF32-AE16931B8169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C227F664-0B00-43B3-9433-A30556D7759D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29610" yWindow="105" windowWidth="20145" windowHeight="12525" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Age Batch Details" sheetId="1" r:id="rId1"/>
     <sheet name="Age Batch Containers" sheetId="2" r:id="rId2"/>
     <sheet name="Pivot" sheetId="7" r:id="rId3"/>
-    <sheet name="Age Scale Read" sheetId="3" r:id="rId4"/>
-    <sheet name="Archive Bin" sheetId="4" r:id="rId5"/>
-    <sheet name="Archive Transfer" sheetId="5" r:id="rId6"/>
-    <sheet name="Glossary" sheetId="6" r:id="rId7"/>
+    <sheet name="FSC_table" sheetId="9" r:id="rId4"/>
+    <sheet name="Age Scale Read" sheetId="3" r:id="rId5"/>
+    <sheet name="Archive Bin" sheetId="4" r:id="rId6"/>
+    <sheet name="Archive Transfer" sheetId="5" r:id="rId7"/>
+    <sheet name="Glossary" sheetId="6" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Age Scale Read'!$A$1:$S$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Age Scale Read'!$A$1:$S$1</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId8"/>
+    <pivotCache cacheId="20" r:id="rId9"/>
   </pivotCaches>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7278" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7295" uniqueCount="351">
   <si>
     <t>BATCH ID</t>
   </si>
@@ -1092,6 +1106,12 @@
   <si>
     <t>md1bcr</t>
   </si>
+  <si>
+    <t>(Multiple Items)</t>
+  </si>
+  <si>
+    <t>total</t>
+  </si>
 </sst>
 </file>
 
@@ -1100,7 +1120,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1109,6 +1129,11 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1146,7 +1171,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1170,6 +1195,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="2"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1188,19 +1214,20 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Strother, Ivy" refreshedDate="46069.482243055558" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="414" xr:uid="{3967CD6F-56B5-4C91-B43B-FA1C69547DD2}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="McGivney, Kate" refreshedDate="46182.489694328702" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="457" xr:uid="{3967CD6F-56B5-4C91-B43B-FA1C69547DD2}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:S1048576" sheet="Age Scale Read"/>
   </cacheSource>
   <cacheFields count="19">
     <cacheField name="BATCH ID" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="101623" maxValue="131287"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="101623" maxValue="141539"/>
     </cacheField>
     <cacheField name="SAMPLE YEAR" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="2022" maxValue="2024" count="4">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="2022" maxValue="2025" count="5">
         <n v="2022"/>
         <n v="2023"/>
         <n v="2024"/>
+        <n v="2025"/>
         <m/>
       </sharedItems>
     </cacheField>
@@ -1260,25 +1287,10 @@
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="94"/>
     </cacheField>
     <cacheField name="EU AGE" numFmtId="0">
-      <sharedItems containsBlank="1" count="8">
-        <s v="12"/>
-        <m/>
-        <s v="11"/>
-        <s v="02"/>
-        <s v="13"/>
-        <s v="03"/>
-        <s v="22"/>
-        <s v="23"/>
-      </sharedItems>
+      <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="PARTIAL AGE" numFmtId="0">
-      <sharedItems containsBlank="1" count="5">
-        <m/>
-        <s v="M2"/>
-        <s v="M3"/>
-        <s v="F1"/>
-        <s v="F0"/>
-      </sharedItems>
+      <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="SCALE CONDITION DESCRIPTION" numFmtId="0">
       <sharedItems containsBlank="1"/>
@@ -1287,7 +1299,7 @@
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="GR AGE" numFmtId="0">
-      <sharedItems containsBlank="1" count="12">
+      <sharedItems containsBlank="1" count="13">
         <s v="42"/>
         <m/>
         <s v="2M"/>
@@ -1300,6 +1312,7 @@
         <s v="53"/>
         <s v="63"/>
         <s v="0F"/>
+        <s v="1M"/>
       </sharedItems>
     </cacheField>
   </cacheFields>
@@ -1312,7 +1325,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="414">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="457">
   <r>
     <n v="102061"/>
     <x v="0"/>
@@ -1328,8 +1341,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="1"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -1349,8 +1362,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="2"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -1370,8 +1383,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="3"/>
-    <x v="1"/>
-    <x v="0"/>
+    <m/>
+    <m/>
     <s v="Regenerate Scale"/>
     <m/>
     <x v="1"/>
@@ -1391,8 +1404,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="4"/>
-    <x v="1"/>
-    <x v="1"/>
+    <m/>
+    <s v="M2"/>
     <s v="Regenerate Scale"/>
     <m/>
     <x v="2"/>
@@ -1412,8 +1425,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="5"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -1433,8 +1446,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="6"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -1454,8 +1467,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="7"/>
-    <x v="2"/>
-    <x v="0"/>
+    <s v="11"/>
+    <m/>
     <m/>
     <m/>
     <x v="3"/>
@@ -1475,8 +1488,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="8"/>
-    <x v="1"/>
-    <x v="0"/>
+    <m/>
+    <m/>
     <s v="Mixed Fish"/>
     <m/>
     <x v="1"/>
@@ -1496,8 +1509,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="9"/>
-    <x v="1"/>
-    <x v="1"/>
+    <m/>
+    <s v="M2"/>
     <s v="Regenerate Scale"/>
     <m/>
     <x v="2"/>
@@ -1517,8 +1530,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="10"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -1538,8 +1551,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="11"/>
-    <x v="1"/>
-    <x v="1"/>
+    <m/>
+    <s v="M2"/>
     <s v="Regenerate Scale"/>
     <m/>
     <x v="2"/>
@@ -1559,8 +1572,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="12"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -1580,8 +1593,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="13"/>
-    <x v="3"/>
-    <x v="0"/>
+    <s v="02"/>
+    <m/>
     <m/>
     <m/>
     <x v="4"/>
@@ -1601,8 +1614,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="14"/>
-    <x v="1"/>
-    <x v="0"/>
+    <m/>
+    <m/>
     <s v="Regenerate Scale"/>
     <m/>
     <x v="1"/>
@@ -1622,8 +1635,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="15"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -1643,8 +1656,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="16"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <m/>
     <x v="5"/>
@@ -1664,8 +1677,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="17"/>
-    <x v="2"/>
-    <x v="0"/>
+    <s v="11"/>
+    <m/>
     <m/>
     <m/>
     <x v="3"/>
@@ -1685,8 +1698,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="18"/>
-    <x v="1"/>
-    <x v="2"/>
+    <m/>
+    <s v="M3"/>
     <s v="Regenerate Scale"/>
     <m/>
     <x v="6"/>
@@ -1706,8 +1719,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="19"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <m/>
     <x v="5"/>
@@ -1727,8 +1740,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="20"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -1748,8 +1761,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="21"/>
-    <x v="1"/>
-    <x v="0"/>
+    <m/>
+    <m/>
     <s v="Regenerate Scale"/>
     <m/>
     <x v="1"/>
@@ -1769,8 +1782,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="22"/>
-    <x v="1"/>
-    <x v="0"/>
+    <m/>
+    <m/>
     <s v="Regenerate Scale"/>
     <m/>
     <x v="1"/>
@@ -1790,8 +1803,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="23"/>
-    <x v="1"/>
-    <x v="0"/>
+    <m/>
+    <m/>
     <s v="Upside Down"/>
     <m/>
     <x v="1"/>
@@ -1811,8 +1824,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="24"/>
-    <x v="1"/>
-    <x v="0"/>
+    <m/>
+    <m/>
     <s v="Upside Down"/>
     <m/>
     <x v="1"/>
@@ -1832,8 +1845,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="25"/>
-    <x v="1"/>
-    <x v="0"/>
+    <m/>
+    <m/>
     <s v="Upside Down"/>
     <m/>
     <x v="1"/>
@@ -1853,8 +1866,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="1"/>
-    <x v="1"/>
-    <x v="0"/>
+    <m/>
+    <m/>
     <s v="Upside Down"/>
     <m/>
     <x v="1"/>
@@ -1874,8 +1887,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="2"/>
-    <x v="1"/>
-    <x v="2"/>
+    <m/>
+    <s v="M3"/>
     <s v="Regenerate Scale"/>
     <m/>
     <x v="6"/>
@@ -1895,8 +1908,8 @@
     <s v="Drift Net"/>
     <s v="Scales"/>
     <n v="1"/>
-    <x v="1"/>
-    <x v="1"/>
+    <m/>
+    <s v="M2"/>
     <s v="Wet Scale"/>
     <m/>
     <x v="2"/>
@@ -1916,8 +1929,8 @@
     <s v="Drift Net"/>
     <s v="Scales"/>
     <n v="2"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -1937,8 +1950,8 @@
     <s v="Drift Net"/>
     <s v="Scales"/>
     <n v="3"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -1958,8 +1971,8 @@
     <s v="Drift Net"/>
     <s v="Scales"/>
     <n v="4"/>
-    <x v="1"/>
-    <x v="0"/>
+    <m/>
+    <m/>
     <s v="Upside Down"/>
     <m/>
     <x v="1"/>
@@ -1979,8 +1992,8 @@
     <s v="Drift Net"/>
     <s v="Scales"/>
     <n v="5"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="5"/>
@@ -2000,8 +2013,8 @@
     <s v="Drift Net"/>
     <s v="Scales"/>
     <n v="6"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -2021,8 +2034,8 @@
     <s v="Drift Net"/>
     <s v="Scales"/>
     <n v="7"/>
-    <x v="1"/>
-    <x v="1"/>
+    <m/>
+    <s v="M2"/>
     <s v="Wet Scale"/>
     <m/>
     <x v="2"/>
@@ -2042,8 +2055,8 @@
     <s v="Drift Net"/>
     <s v="Scales"/>
     <n v="1"/>
-    <x v="1"/>
-    <x v="0"/>
+    <m/>
+    <m/>
     <s v="No Structure"/>
     <m/>
     <x v="1"/>
@@ -2063,8 +2076,8 @@
     <s v="Drift Net"/>
     <s v="Scales"/>
     <n v="2"/>
-    <x v="1"/>
-    <x v="0"/>
+    <m/>
+    <m/>
     <s v="No Structure"/>
     <m/>
     <x v="1"/>
@@ -2084,8 +2097,8 @@
     <s v="Drift Net"/>
     <s v="Scales"/>
     <n v="3"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -2105,8 +2118,8 @@
     <s v="Drift Net"/>
     <s v="Scales"/>
     <n v="4"/>
-    <x v="1"/>
-    <x v="0"/>
+    <m/>
+    <m/>
     <s v="Upside Down"/>
     <m/>
     <x v="1"/>
@@ -2126,8 +2139,8 @@
     <s v="Drift Net"/>
     <s v="Scales"/>
     <n v="5"/>
-    <x v="1"/>
-    <x v="0"/>
+    <m/>
+    <m/>
     <s v="Upside Down"/>
     <m/>
     <x v="1"/>
@@ -2147,8 +2160,8 @@
     <s v="Drift Net"/>
     <s v="Scales"/>
     <n v="6"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -2168,8 +2181,8 @@
     <s v="Drift Net"/>
     <s v="Scales"/>
     <n v="1"/>
-    <x v="1"/>
-    <x v="2"/>
+    <m/>
+    <s v="M3"/>
     <s v="Regenerate Scale"/>
     <m/>
     <x v="6"/>
@@ -2189,8 +2202,8 @@
     <s v="Drift Net"/>
     <s v="Scales"/>
     <n v="2"/>
-    <x v="1"/>
-    <x v="0"/>
+    <m/>
+    <m/>
     <s v="Upside Down"/>
     <m/>
     <x v="1"/>
@@ -2210,8 +2223,8 @@
     <s v="Drift Net"/>
     <s v="Scales"/>
     <n v="3"/>
-    <x v="1"/>
-    <x v="2"/>
+    <m/>
+    <s v="M3"/>
     <s v="Regenerate Scale"/>
     <m/>
     <x v="6"/>
@@ -2231,8 +2244,8 @@
     <s v="Drift Net"/>
     <s v="Scales"/>
     <n v="4"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -2252,8 +2265,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="1"/>
-    <x v="1"/>
-    <x v="2"/>
+    <m/>
+    <s v="M3"/>
     <m/>
     <m/>
     <x v="6"/>
@@ -2273,8 +2286,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="2"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <m/>
     <x v="5"/>
@@ -2294,8 +2307,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="3"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -2315,8 +2328,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="4"/>
-    <x v="1"/>
-    <x v="0"/>
+    <m/>
+    <m/>
     <s v="Mixed Fish"/>
     <m/>
     <x v="1"/>
@@ -2336,8 +2349,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="5"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -2357,8 +2370,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="6"/>
-    <x v="5"/>
-    <x v="0"/>
+    <s v="03"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="7"/>
@@ -2378,8 +2391,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="7"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -2399,8 +2412,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="8"/>
-    <x v="5"/>
-    <x v="0"/>
+    <s v="03"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="7"/>
@@ -2420,8 +2433,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="9"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -2441,8 +2454,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="10"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -2462,8 +2475,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="11"/>
-    <x v="1"/>
-    <x v="0"/>
+    <m/>
+    <m/>
     <s v="Regenerate Scale"/>
     <m/>
     <x v="1"/>
@@ -2483,8 +2496,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="12"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -2504,8 +2517,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="1"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <m/>
     <x v="5"/>
@@ -2525,8 +2538,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="2"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -2546,8 +2559,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="3"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -2567,8 +2580,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="4"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -2588,8 +2601,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="5"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -2609,8 +2622,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="6"/>
-    <x v="1"/>
-    <x v="0"/>
+    <m/>
+    <m/>
     <s v="2 structures; ages do no agree/another abbrev. does not provide the reason"/>
     <m/>
     <x v="1"/>
@@ -2630,8 +2643,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="7"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -2651,8 +2664,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="8"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -2672,8 +2685,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="9"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <m/>
     <x v="5"/>
@@ -2693,8 +2706,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="10"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -2714,8 +2727,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="11"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -2735,8 +2748,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="12"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -2756,8 +2769,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="13"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -2777,8 +2790,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="14"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -2798,8 +2811,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="1"/>
-    <x v="1"/>
-    <x v="3"/>
+    <m/>
+    <s v="F1"/>
     <m/>
     <m/>
     <x v="8"/>
@@ -2819,8 +2832,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="2"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -2840,8 +2853,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="3"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -2861,8 +2874,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="4"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -2882,8 +2895,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="5"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -2903,8 +2916,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="6"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -2924,8 +2937,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="7"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -2945,8 +2958,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="8"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -2966,8 +2979,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="9"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -2987,8 +3000,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="10"/>
-    <x v="1"/>
-    <x v="3"/>
+    <m/>
+    <s v="F1"/>
     <m/>
     <m/>
     <x v="8"/>
@@ -3008,8 +3021,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="11"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <m/>
     <x v="5"/>
@@ -3029,8 +3042,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="12"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -3050,8 +3063,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="13"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="5"/>
@@ -3071,8 +3084,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="14"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -3092,8 +3105,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="15"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -3113,8 +3126,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="1"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -3134,8 +3147,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="2"/>
-    <x v="1"/>
-    <x v="3"/>
+    <m/>
+    <s v="F1"/>
     <m/>
     <m/>
     <x v="8"/>
@@ -3155,8 +3168,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="3"/>
-    <x v="1"/>
-    <x v="3"/>
+    <m/>
+    <s v="F1"/>
     <m/>
     <m/>
     <x v="8"/>
@@ -3176,8 +3189,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="1"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -3197,8 +3210,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="2"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <m/>
     <x v="5"/>
@@ -3218,8 +3231,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="1"/>
-    <x v="1"/>
-    <x v="3"/>
+    <m/>
+    <s v="F1"/>
     <s v="Resorbed Scale"/>
     <s v="Unknown amount of resorption. Cannot assess the number of marine annuli missing. Only freshwater age given, no marine age given."/>
     <x v="8"/>
@@ -3239,8 +3252,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="2"/>
-    <x v="1"/>
-    <x v="1"/>
+    <m/>
+    <s v="M2"/>
     <s v="Regenerate Scale"/>
     <s v="Resorbed Age Interpretation. Resorption affecting age and missing 1 marine annulus"/>
     <x v="2"/>
@@ -3260,8 +3273,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="3"/>
-    <x v="1"/>
-    <x v="1"/>
+    <m/>
+    <s v="M2"/>
     <s v="Regenerate Scale"/>
     <s v="Resorbed Age Interpretation. Resorption affecting age and missing 1 marine annulus"/>
     <x v="2"/>
@@ -3281,8 +3294,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="4"/>
-    <x v="1"/>
-    <x v="3"/>
+    <m/>
+    <s v="F1"/>
     <s v="Resorbed Scale"/>
     <s v="Unknown amount of resorption. Cannot assess the number of marine annuli missing. Only freshwater age given, no marine age given."/>
     <x v="8"/>
@@ -3302,8 +3315,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="5"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorbed Age Interpretation. Resorption affecting age and missing 1 marine annulus"/>
     <x v="0"/>
@@ -3323,8 +3336,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="6"/>
-    <x v="1"/>
-    <x v="3"/>
+    <m/>
+    <s v="F1"/>
     <s v="Resorbed Scale"/>
     <s v="Unknown amount of resorption. Cannot assess the number of marine annuli missing. Only freshwater age given, no marine age given."/>
     <x v="8"/>
@@ -3344,8 +3357,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="7"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorbed Age Interpretation. Resorption affecting age and missing 1 marine annulus"/>
     <x v="0"/>
@@ -3365,8 +3378,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="8"/>
-    <x v="1"/>
-    <x v="3"/>
+    <m/>
+    <s v="F1"/>
     <s v="Resorbed Scale"/>
     <s v="Unknown amount of resorption. Cannot assess the number of marine annuli missing. Only freshwater age given, no marine age given."/>
     <x v="8"/>
@@ -3386,8 +3399,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="9"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorbed Age Interpretation. Resorption affecting age and missing 1 marine annulus"/>
     <x v="0"/>
@@ -3407,8 +3420,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="10"/>
-    <x v="1"/>
-    <x v="3"/>
+    <m/>
+    <s v="F1"/>
     <s v="Resorbed Scale"/>
     <s v="Unknown amount of resorption. Cannot assess the number of marine annuli missing. Only freshwater age given, no marine age given."/>
     <x v="8"/>
@@ -3428,8 +3441,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="1"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="5"/>
@@ -3449,8 +3462,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="2"/>
-    <x v="2"/>
-    <x v="0"/>
+    <s v="11"/>
+    <m/>
     <m/>
     <s v="Resorbed Age Interpretation. Resorption affecting age and missing 1 marine annulus"/>
     <x v="3"/>
@@ -3470,8 +3483,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="3"/>
-    <x v="1"/>
-    <x v="3"/>
+    <m/>
+    <s v="F1"/>
     <s v="Resorbed Scale"/>
     <s v="Unknown amount of resorption. Cannot assess the number of marine annuli missing. Only freshwater age given, no marine age given."/>
     <x v="8"/>
@@ -3491,8 +3504,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="4"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="5"/>
@@ -3512,8 +3525,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="5"/>
-    <x v="1"/>
-    <x v="3"/>
+    <m/>
+    <s v="F1"/>
     <s v="Resorbed Scale"/>
     <s v="Unknown amount of resorption. Cannot assess the number of marine annuli missing. Only freshwater age given, no marine age given."/>
     <x v="8"/>
@@ -3533,8 +3546,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="6"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorbed Age Interpretation. Resorption affecting age and missing 1 marine annulus"/>
     <x v="0"/>
@@ -3554,8 +3567,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="7"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorbed Age Interpretation. Resorption affecting age and missing 1 marine annulus"/>
     <x v="0"/>
@@ -3575,8 +3588,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="8"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorbed Age Interpretation. Resorption affecting age and missing 1 marine annulus"/>
     <x v="0"/>
@@ -3596,8 +3609,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="9"/>
-    <x v="1"/>
-    <x v="0"/>
+    <m/>
+    <m/>
     <s v="Regenerate Scale"/>
     <s v="Unknown amount of resorption. Cannot assess the number of marine annuli missing. Only freshwater age given, no marine age given."/>
     <x v="1"/>
@@ -3617,8 +3630,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="10"/>
-    <x v="1"/>
-    <x v="3"/>
+    <m/>
+    <s v="F1"/>
     <s v="Resorbed Scale"/>
     <s v="Unknown amount of resorption. Cannot assess the number of marine annuli missing. Only freshwater age given, no marine age given."/>
     <x v="8"/>
@@ -3638,8 +3651,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="1"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorbed Age Interpretation. Resorption affecting age and missing 1 marine annulus"/>
     <x v="0"/>
@@ -3659,8 +3672,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="2"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorbed Age Interpretation. Resorption affecting age and missing 1 marine annulus"/>
     <x v="0"/>
@@ -3680,8 +3693,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="3"/>
-    <x v="1"/>
-    <x v="3"/>
+    <m/>
+    <s v="F1"/>
     <s v="Resorbed Scale"/>
     <s v="Unknown amount of resorption. Cannot assess the number of marine annuli missing. Only freshwater age given, no marine age given."/>
     <x v="8"/>
@@ -3701,8 +3714,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="4"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -3722,8 +3735,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="5"/>
-    <x v="1"/>
-    <x v="3"/>
+    <m/>
+    <s v="F1"/>
     <s v="Resorbed Scale"/>
     <s v="Unknown amount of resorption. Cannot assess the number of marine annuli missing. Only freshwater age given, no marine age given."/>
     <x v="8"/>
@@ -3743,8 +3756,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="6"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorbed Age Interpretation. Resorption affecting age and missing 1 marine annulus"/>
     <x v="0"/>
@@ -3764,8 +3777,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="7"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorbed Age Interpretation. Resorption affecting age and missing 1 marine annulus"/>
     <x v="0"/>
@@ -3785,8 +3798,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="8"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorbed Age Interpretation. Resorption affecting age and missing 1 marine annulus"/>
     <x v="0"/>
@@ -3806,8 +3819,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="9"/>
-    <x v="1"/>
-    <x v="3"/>
+    <m/>
+    <s v="F1"/>
     <s v="Resorbed Scale"/>
     <s v="Unknown amount of resorption. Cannot assess the number of marine annuli missing. Only freshwater age given, no marine age given."/>
     <x v="8"/>
@@ -3827,8 +3840,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="1"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <m/>
     <x v="5"/>
@@ -3848,8 +3861,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="2"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -3869,8 +3882,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="3"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -3890,8 +3903,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="4"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <m/>
     <x v="5"/>
@@ -3911,8 +3924,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="5"/>
-    <x v="5"/>
-    <x v="0"/>
+    <s v="03"/>
+    <m/>
     <m/>
     <m/>
     <x v="7"/>
@@ -3932,8 +3945,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="1"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorbed Age Interpretation. Resorption affecting age and missing 1 marine annulus"/>
     <x v="0"/>
@@ -3953,8 +3966,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="2"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorbed Age Interpretation. Resorption affecting age and missing 1 marine annulus"/>
     <x v="0"/>
@@ -3974,8 +3987,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="3"/>
-    <x v="1"/>
-    <x v="3"/>
+    <m/>
+    <s v="F1"/>
     <s v="Resorbed Scale"/>
     <s v="Unknown amount of resorption. Cannot assess the number of marine annuli missing. Only freshwater age given, no marine age given."/>
     <x v="8"/>
@@ -3995,8 +4008,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="4"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="5"/>
@@ -4016,8 +4029,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="5"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorbed Age Interpretation. Resorption affecting age and missing 1 marine annulus"/>
     <x v="0"/>
@@ -4037,8 +4050,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="6"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="5"/>
@@ -4058,8 +4071,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="7"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <s v="Resorbed Age Interpretation. Resorption affecting age and missing 1 marine annulus"/>
     <x v="5"/>
@@ -4079,8 +4092,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="1"/>
-    <x v="1"/>
-    <x v="3"/>
+    <m/>
+    <s v="F1"/>
     <s v="Resorbed Scale"/>
     <s v="Unknown amount of resorption. Cannot assess the number of marine annuli missing. Only freshwater age given, no marine age given."/>
     <x v="8"/>
@@ -4100,8 +4113,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="2"/>
-    <x v="1"/>
-    <x v="3"/>
+    <m/>
+    <s v="F1"/>
     <s v="Resorbed Scale"/>
     <s v="Unknown amount of resorption. Cannot assess the number of marine annuli missing. Only freshwater age given, no marine age given."/>
     <x v="8"/>
@@ -4121,8 +4134,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="3"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorbed Age Interpretation. Resorption affecting age and missing 1 marine annulus"/>
     <x v="0"/>
@@ -4142,8 +4155,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="4"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorbed Age Interpretation. Resorption affecting age and missing 1 marine annulus"/>
     <x v="0"/>
@@ -4163,8 +4176,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="5"/>
-    <x v="1"/>
-    <x v="3"/>
+    <m/>
+    <s v="F1"/>
     <s v="Resorbed Scale"/>
     <s v="Unknown amount of resorption. Cannot assess the number of marine annuli missing. Only freshwater age given, no marine age given."/>
     <x v="8"/>
@@ -4184,8 +4197,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="6"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -4205,8 +4218,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="7"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="5"/>
@@ -4226,8 +4239,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="8"/>
-    <x v="1"/>
-    <x v="3"/>
+    <m/>
+    <s v="F1"/>
     <s v="Resorbed Scale"/>
     <s v="Unknown amount of resorption. Cannot assess the number of marine annuli missing. Only freshwater age given, no marine age given."/>
     <x v="8"/>
@@ -4247,8 +4260,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="1"/>
-    <x v="1"/>
-    <x v="0"/>
+    <m/>
+    <m/>
     <s v="No Structure"/>
     <m/>
     <x v="1"/>
@@ -4268,8 +4281,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="2"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -4289,8 +4302,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="3"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <m/>
     <x v="5"/>
@@ -4310,8 +4323,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="1"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -4331,8 +4344,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="2"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -4352,8 +4365,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="3"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -4373,8 +4386,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="4"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -4394,8 +4407,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="5"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -4415,8 +4428,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="6"/>
-    <x v="6"/>
-    <x v="0"/>
+    <s v="22"/>
+    <m/>
     <m/>
     <m/>
     <x v="9"/>
@@ -4436,8 +4449,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="7"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <m/>
     <x v="5"/>
@@ -4457,8 +4470,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="8"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -4478,8 +4491,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="9"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <m/>
     <x v="5"/>
@@ -4499,8 +4512,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="10"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -4520,8 +4533,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="11"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <m/>
     <x v="5"/>
@@ -4541,8 +4554,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="12"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <m/>
     <x v="5"/>
@@ -4562,8 +4575,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="13"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -4583,8 +4596,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="14"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -4604,8 +4617,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="15"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -4625,8 +4638,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="16"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -4646,8 +4659,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="17"/>
-    <x v="6"/>
-    <x v="0"/>
+    <s v="22"/>
+    <m/>
     <m/>
     <m/>
     <x v="9"/>
@@ -4667,8 +4680,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="18"/>
-    <x v="1"/>
-    <x v="0"/>
+    <m/>
+    <m/>
     <s v="No Structure"/>
     <m/>
     <x v="1"/>
@@ -4688,8 +4701,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="19"/>
-    <x v="1"/>
-    <x v="1"/>
+    <m/>
+    <s v="M2"/>
     <s v="Unresolved Freshwater Age"/>
     <m/>
     <x v="2"/>
@@ -4709,8 +4722,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="20"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -4730,8 +4743,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="21"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <m/>
     <x v="5"/>
@@ -4751,8 +4764,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="22"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -4772,8 +4785,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="23"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -4793,8 +4806,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="24"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -4814,8 +4827,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="25"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -4835,8 +4848,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="26"/>
-    <x v="6"/>
-    <x v="0"/>
+    <s v="22"/>
+    <m/>
     <m/>
     <m/>
     <x v="9"/>
@@ -4856,8 +4869,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="27"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -4877,8 +4890,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="28"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -4898,8 +4911,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="29"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -4919,8 +4932,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="30"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -4940,8 +4953,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="31"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -4961,8 +4974,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="32"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -4982,8 +4995,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="33"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -5003,8 +5016,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="34"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <m/>
     <x v="5"/>
@@ -5024,8 +5037,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="35"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <m/>
     <x v="5"/>
@@ -5045,8 +5058,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="36"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -5066,8 +5079,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="37"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <m/>
     <x v="5"/>
@@ -5087,8 +5100,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="38"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorbed Age Interpretation. Resorption affecting age and missing 1 marine annulus"/>
     <x v="0"/>
@@ -5108,8 +5121,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="39"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -5129,8 +5142,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="40"/>
-    <x v="7"/>
-    <x v="0"/>
+    <s v="23"/>
+    <m/>
     <m/>
     <m/>
     <x v="10"/>
@@ -5150,8 +5163,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="41"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -5171,8 +5184,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="42"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -5192,8 +5205,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="43"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -5213,8 +5226,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="44"/>
-    <x v="1"/>
-    <x v="0"/>
+    <m/>
+    <m/>
     <s v="No Structure"/>
     <m/>
     <x v="1"/>
@@ -5234,8 +5247,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="45"/>
-    <x v="1"/>
-    <x v="0"/>
+    <m/>
+    <m/>
     <s v="No Structure"/>
     <m/>
     <x v="1"/>
@@ -5255,8 +5268,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="46"/>
-    <x v="1"/>
-    <x v="0"/>
+    <m/>
+    <m/>
     <s v="No Structure"/>
     <m/>
     <x v="1"/>
@@ -5276,8 +5289,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="47"/>
-    <x v="1"/>
-    <x v="0"/>
+    <m/>
+    <m/>
     <s v="No Structure"/>
     <m/>
     <x v="1"/>
@@ -5297,8 +5310,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="48"/>
-    <x v="1"/>
-    <x v="0"/>
+    <m/>
+    <m/>
     <s v="No Structure"/>
     <m/>
     <x v="1"/>
@@ -5318,8 +5331,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="49"/>
-    <x v="1"/>
-    <x v="0"/>
+    <m/>
+    <m/>
     <s v="No Structure"/>
     <m/>
     <x v="1"/>
@@ -5339,8 +5352,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="50"/>
-    <x v="1"/>
-    <x v="0"/>
+    <m/>
+    <m/>
     <s v="No Structure"/>
     <m/>
     <x v="1"/>
@@ -5360,8 +5373,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="51"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -5381,8 +5394,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="52"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <m/>
     <x v="5"/>
@@ -5402,8 +5415,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="53"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -5423,8 +5436,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="54"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -5444,8 +5457,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="55"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <m/>
     <x v="5"/>
@@ -5465,8 +5478,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="56"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -5486,8 +5499,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="57"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <m/>
     <x v="5"/>
@@ -5507,8 +5520,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="58"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -5528,8 +5541,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="59"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <m/>
     <x v="5"/>
@@ -5549,8 +5562,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="60"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -5570,8 +5583,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="61"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <m/>
     <x v="5"/>
@@ -5591,8 +5604,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="62"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -5612,8 +5625,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="63"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -5633,8 +5646,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="64"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -5654,8 +5667,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="65"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <m/>
     <x v="5"/>
@@ -5675,8 +5688,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="66"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <m/>
     <x v="5"/>
@@ -5696,8 +5709,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="67"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -5717,8 +5730,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="68"/>
-    <x v="5"/>
-    <x v="0"/>
+    <s v="03"/>
+    <m/>
     <m/>
     <m/>
     <x v="7"/>
@@ -5738,8 +5751,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="69"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -5759,8 +5772,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="70"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -5780,8 +5793,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="71"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <m/>
     <x v="5"/>
@@ -5801,8 +5814,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="72"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <m/>
     <x v="5"/>
@@ -5822,8 +5835,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="73"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <m/>
     <x v="5"/>
@@ -5843,8 +5856,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="74"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <m/>
     <x v="5"/>
@@ -5864,8 +5877,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="75"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -5885,8 +5898,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="76"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <m/>
     <x v="5"/>
@@ -5906,8 +5919,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="77"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -5927,8 +5940,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="78"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -5948,8 +5961,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="79"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -5969,8 +5982,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="80"/>
-    <x v="7"/>
-    <x v="0"/>
+    <s v="23"/>
+    <m/>
     <m/>
     <m/>
     <x v="10"/>
@@ -5990,8 +6003,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="81"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -6011,8 +6024,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="82"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -6032,8 +6045,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="83"/>
-    <x v="1"/>
-    <x v="3"/>
+    <m/>
+    <s v="F1"/>
     <s v="Resorbed Scale"/>
     <s v="Unknown amount of resorption. Cannot assess the number of marine annuli missing. Only freshwater age given, no marine age given."/>
     <x v="8"/>
@@ -6053,8 +6066,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="84"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <m/>
     <x v="5"/>
@@ -6074,8 +6087,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="85"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -6095,8 +6108,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="86"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -6116,8 +6129,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="87"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <m/>
     <x v="5"/>
@@ -6137,8 +6150,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="88"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -6158,8 +6171,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="89"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <m/>
     <x v="5"/>
@@ -6179,8 +6192,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="90"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -6200,8 +6213,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="91"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -6221,8 +6234,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="92"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -6242,8 +6255,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="93"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <m/>
     <x v="5"/>
@@ -6263,8 +6276,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="1"/>
-    <x v="5"/>
-    <x v="0"/>
+    <s v="03"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="7"/>
@@ -6284,8 +6297,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="2"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -6305,8 +6318,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="3"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -6326,8 +6339,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="4"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -6347,8 +6360,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="5"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -6368,8 +6381,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="6"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -6389,8 +6402,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="7"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -6410,8 +6423,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="8"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <m/>
     <x v="5"/>
@@ -6431,8 +6444,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="9"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -6452,8 +6465,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="10"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -6473,8 +6486,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="11"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -6494,8 +6507,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="12"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -6515,8 +6528,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="13"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="5"/>
@@ -6536,8 +6549,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="14"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -6557,8 +6570,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="15"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <m/>
     <x v="5"/>
@@ -6578,8 +6591,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="16"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <m/>
     <x v="5"/>
@@ -6599,8 +6612,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="17"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="5"/>
@@ -6620,8 +6633,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="18"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -6641,8 +6654,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="19"/>
-    <x v="5"/>
-    <x v="0"/>
+    <s v="03"/>
+    <m/>
     <m/>
     <m/>
     <x v="7"/>
@@ -6662,8 +6675,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="20"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -6683,8 +6696,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="21"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -6704,8 +6717,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="22"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -6725,8 +6738,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="23"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -6746,8 +6759,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="24"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -6767,8 +6780,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="25"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -6788,8 +6801,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="26"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <m/>
     <x v="5"/>
@@ -6809,8 +6822,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="27"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -6830,8 +6843,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="28"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="5"/>
@@ -6851,8 +6864,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="29"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -6872,8 +6885,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="30"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -6893,8 +6906,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="31"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -6914,8 +6927,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="32"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -6935,8 +6948,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="33"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -6956,8 +6969,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="34"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -6977,8 +6990,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="35"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -6998,8 +7011,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="36"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -7019,8 +7032,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="37"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="5"/>
@@ -7040,8 +7053,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="38"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -7061,8 +7074,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="39"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <m/>
     <x v="5"/>
@@ -7082,8 +7095,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="40"/>
-    <x v="5"/>
-    <x v="0"/>
+    <s v="03"/>
+    <m/>
     <m/>
     <m/>
     <x v="7"/>
@@ -7103,8 +7116,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="41"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <m/>
     <x v="5"/>
@@ -7124,8 +7137,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="42"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -7145,8 +7158,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="43"/>
-    <x v="1"/>
-    <x v="0"/>
+    <m/>
+    <m/>
     <s v="No Structure"/>
     <m/>
     <x v="1"/>
@@ -7166,8 +7179,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="44"/>
-    <x v="1"/>
-    <x v="0"/>
+    <m/>
+    <m/>
     <s v="No Structure"/>
     <m/>
     <x v="1"/>
@@ -7187,8 +7200,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="45"/>
-    <x v="1"/>
-    <x v="0"/>
+    <m/>
+    <m/>
     <s v="No Structure"/>
     <m/>
     <x v="1"/>
@@ -7208,8 +7221,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="46"/>
-    <x v="1"/>
-    <x v="0"/>
+    <m/>
+    <m/>
     <s v="No Structure"/>
     <m/>
     <x v="1"/>
@@ -7229,8 +7242,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="47"/>
-    <x v="1"/>
-    <x v="0"/>
+    <m/>
+    <m/>
     <s v="No Structure"/>
     <m/>
     <x v="1"/>
@@ -7250,8 +7263,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="48"/>
-    <x v="1"/>
-    <x v="0"/>
+    <m/>
+    <m/>
     <s v="No Structure"/>
     <m/>
     <x v="1"/>
@@ -7271,8 +7284,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="49"/>
-    <x v="1"/>
-    <x v="0"/>
+    <m/>
+    <m/>
     <s v="No Structure"/>
     <m/>
     <x v="1"/>
@@ -7292,8 +7305,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="50"/>
-    <x v="1"/>
-    <x v="0"/>
+    <m/>
+    <m/>
     <s v="No Structure"/>
     <m/>
     <x v="1"/>
@@ -7313,8 +7326,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="51"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -7334,8 +7347,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="52"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -7355,8 +7368,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="53"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -7376,8 +7389,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="54"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -7397,8 +7410,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="55"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -7418,8 +7431,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="56"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <m/>
     <x v="5"/>
@@ -7439,8 +7452,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="57"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -7460,8 +7473,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="58"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -7481,8 +7494,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="59"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -7502,8 +7515,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="60"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -7523,8 +7536,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="61"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -7544,8 +7557,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="62"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -7565,8 +7578,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="63"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -7586,8 +7599,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="64"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="5"/>
@@ -7607,8 +7620,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="65"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -7628,8 +7641,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="66"/>
-    <x v="2"/>
-    <x v="0"/>
+    <s v="11"/>
+    <m/>
     <m/>
     <m/>
     <x v="3"/>
@@ -7649,8 +7662,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="67"/>
-    <x v="5"/>
-    <x v="0"/>
+    <s v="03"/>
+    <m/>
     <m/>
     <m/>
     <x v="7"/>
@@ -7670,8 +7683,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="68"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -7691,8 +7704,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="69"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="5"/>
@@ -7712,8 +7725,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="70"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="5"/>
@@ -7733,8 +7746,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="71"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -7754,8 +7767,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="72"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -7775,8 +7788,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="73"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -7796,8 +7809,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="74"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -7817,8 +7830,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="75"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -7838,8 +7851,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="76"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -7859,8 +7872,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="77"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -7880,8 +7893,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="78"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -7901,8 +7914,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="79"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -7922,8 +7935,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="80"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -7943,8 +7956,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="81"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -7964,8 +7977,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="82"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="5"/>
@@ -7985,8 +7998,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="83"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -8006,8 +8019,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="84"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -8027,8 +8040,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="85"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -8048,8 +8061,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="86"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -8069,8 +8082,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="87"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -8090,8 +8103,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="88"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -8111,8 +8124,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="89"/>
-    <x v="5"/>
-    <x v="0"/>
+    <s v="03"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="7"/>
@@ -8132,8 +8145,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="90"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -8153,8 +8166,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="91"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -8174,8 +8187,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="92"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -8195,8 +8208,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="93"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -8216,8 +8229,8 @@
     <s v="Gillnet"/>
     <s v="Otoliths and Scales"/>
     <n v="94"/>
-    <x v="5"/>
-    <x v="0"/>
+    <s v="03"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="7"/>
@@ -8237,8 +8250,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="1"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="5"/>
@@ -8258,8 +8271,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="2"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="5"/>
@@ -8279,8 +8292,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="3"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="5"/>
@@ -8300,8 +8313,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="4"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="5"/>
@@ -8321,8 +8334,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="5"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="5"/>
@@ -8342,8 +8355,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="6"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -8363,8 +8376,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="7"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="5"/>
@@ -8384,8 +8397,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="8"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -8405,8 +8418,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="9"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="5"/>
@@ -8426,8 +8439,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="10"/>
-    <x v="2"/>
-    <x v="0"/>
+    <s v="11"/>
+    <m/>
     <s v="Scale Age - No otolith age expected"/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="3"/>
@@ -8447,8 +8460,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="1"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -8468,8 +8481,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="1"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -8489,8 +8502,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="2"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorbed Age Interpretation. Resorption affecting age and missing 1 marine annulus"/>
     <x v="0"/>
@@ -8510,8 +8523,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="3"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <s v="Resorbed Age Interpretation. Resorption affecting age and missing 1 marine annulus"/>
     <x v="5"/>
@@ -8531,8 +8544,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="4"/>
-    <x v="1"/>
-    <x v="3"/>
+    <m/>
+    <s v="F1"/>
     <s v="Resorbed Scale"/>
     <s v="Unknown amount of resorption. Cannot assess the number of marine annuli missing. Only freshwater age given, no marine age given."/>
     <x v="8"/>
@@ -8552,8 +8565,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="5"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <s v="Resorbed Age Interpretation. Resorption affecting age and missing 1 marine annulus"/>
     <x v="5"/>
@@ -8573,8 +8586,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="6"/>
-    <x v="2"/>
-    <x v="0"/>
+    <s v="11"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="3"/>
@@ -8594,8 +8607,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="7"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -8615,8 +8628,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="8"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <s v="Resorbed Age Interpretation. Resorption affecting age and missing 1 marine annulus"/>
     <x v="5"/>
@@ -8636,8 +8649,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="9"/>
-    <x v="1"/>
-    <x v="3"/>
+    <m/>
+    <s v="F1"/>
     <s v="Resorbed Scale"/>
     <s v="Unknown amount of resorption. Cannot assess the number of marine annuli missing. Only freshwater age given, no marine age given."/>
     <x v="8"/>
@@ -8657,8 +8670,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="10"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorbed Age Interpretation. Resorption affecting age and missing 1 marine annulus"/>
     <x v="0"/>
@@ -8678,8 +8691,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="11"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorbed Age Interpretation. Resorption affecting age and missing 1 marine annulus"/>
     <x v="0"/>
@@ -8699,8 +8712,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="12"/>
-    <x v="1"/>
-    <x v="2"/>
+    <m/>
+    <s v="M3"/>
     <s v="Regenerate Scale"/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="6"/>
@@ -8720,8 +8733,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="13"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -8741,8 +8754,8 @@
     <s v="Gillnet"/>
     <s v="Scales"/>
     <n v="14"/>
-    <x v="1"/>
-    <x v="3"/>
+    <m/>
+    <s v="F1"/>
     <s v="Resorbed Scale"/>
     <s v="Unknown amount of resorption. Cannot assess the number of marine annuli missing. Only freshwater age given, no marine age given."/>
     <x v="8"/>
@@ -8762,8 +8775,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="1"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="5"/>
@@ -8783,8 +8796,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="2"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -8804,8 +8817,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="3"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -8825,8 +8838,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="4"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -8846,8 +8859,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="5"/>
-    <x v="3"/>
-    <x v="0"/>
+    <s v="02"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="4"/>
@@ -8867,8 +8880,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="6"/>
-    <x v="3"/>
-    <x v="0"/>
+    <s v="02"/>
+    <m/>
     <m/>
     <m/>
     <x v="4"/>
@@ -8888,8 +8901,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="7"/>
-    <x v="3"/>
-    <x v="0"/>
+    <s v="02"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="4"/>
@@ -8909,8 +8922,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="8"/>
-    <x v="1"/>
-    <x v="4"/>
+    <m/>
+    <s v="F0"/>
     <s v="Resorbed Scale"/>
     <s v="Unknown amount of resorption. Cannot assess the number of marine annuli missing. Only freshwater age given, no marine age given."/>
     <x v="11"/>
@@ -8930,8 +8943,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="9"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="13"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="5"/>
@@ -8951,8 +8964,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="10"/>
-    <x v="1"/>
-    <x v="3"/>
+    <m/>
+    <s v="F1"/>
     <s v="Resorbed Scale"/>
     <s v="Unknown amount of resorption. Cannot assess the number of marine annuli missing. Only freshwater age given, no marine age given."/>
     <x v="8"/>
@@ -8972,8 +8985,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="11"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -8993,8 +9006,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="12"/>
-    <x v="1"/>
-    <x v="3"/>
+    <m/>
+    <s v="F1"/>
     <s v="Resorbed Scale"/>
     <s v="Unknown amount of resorption. Cannot assess the number of marine annuli missing. Only freshwater age given, no marine age given."/>
     <x v="8"/>
@@ -9014,8 +9027,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="13"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -9035,8 +9048,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="14"/>
-    <x v="1"/>
-    <x v="3"/>
+    <m/>
+    <s v="F1"/>
     <s v="Resorbed Scale"/>
     <s v="Unknown amount of resorption. Cannot assess the number of marine annuli missing. Only freshwater age given, no marine age given."/>
     <x v="8"/>
@@ -9056,8 +9069,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="15"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -9077,8 +9090,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="16"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -9098,8 +9111,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="17"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -9119,8 +9132,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="18"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <m/>
     <x v="0"/>
@@ -9140,8 +9153,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="19"/>
-    <x v="1"/>
-    <x v="3"/>
+    <m/>
+    <s v="F1"/>
     <s v="Resorbed Scale"/>
     <s v="Unknown amount of resorption. Cannot assess the number of marine annuli missing. Only freshwater age given, no marine age given."/>
     <x v="8"/>
@@ -9161,8 +9174,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="20"/>
-    <x v="3"/>
-    <x v="0"/>
+    <s v="02"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="4"/>
@@ -9182,8 +9195,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="21"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -9203,8 +9216,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="22"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -9224,8 +9237,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="23"/>
-    <x v="1"/>
-    <x v="3"/>
+    <m/>
+    <s v="F1"/>
     <s v="Resorbed Scale"/>
     <s v="Unknown amount of resorption. Cannot assess the number of marine annuli missing. Only freshwater age given, no marine age given."/>
     <x v="8"/>
@@ -9245,8 +9258,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="24"/>
-    <x v="1"/>
-    <x v="4"/>
+    <m/>
+    <s v="F0"/>
     <s v="Resorbed Scale"/>
     <m/>
     <x v="11"/>
@@ -9266,8 +9279,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="25"/>
-    <x v="1"/>
-    <x v="3"/>
+    <m/>
+    <s v="F1"/>
     <s v="Resorbed Scale"/>
     <m/>
     <x v="8"/>
@@ -9287,8 +9300,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="1"/>
-    <x v="1"/>
-    <x v="3"/>
+    <m/>
+    <s v="F1"/>
     <s v="Resorbed Scale"/>
     <s v="Unknown amount of resorption. Cannot assess the number of marine annuli missing. Only freshwater age given, no marine age given."/>
     <x v="8"/>
@@ -9308,8 +9321,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="2"/>
-    <x v="1"/>
-    <x v="3"/>
+    <m/>
+    <s v="F1"/>
     <s v="Resorbed Scale"/>
     <s v="Unknown amount of resorption. Cannot assess the number of marine annuli missing. Only freshwater age given, no marine age given."/>
     <x v="8"/>
@@ -9329,8 +9342,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="3"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -9350,8 +9363,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="4"/>
-    <x v="1"/>
-    <x v="4"/>
+    <m/>
+    <s v="F0"/>
     <s v="Unresolved Marine Age"/>
     <s v="Unknown amount of resorption. Cannot assess the number of marine annuli missing. Only freshwater age given, no marine age given."/>
     <x v="11"/>
@@ -9371,8 +9384,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="5"/>
-    <x v="1"/>
-    <x v="0"/>
+    <m/>
+    <m/>
     <s v="Upside Down"/>
     <m/>
     <x v="1"/>
@@ -9392,8 +9405,8 @@
     <s v="Dip Net"/>
     <s v="Scales"/>
     <n v="1"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -9413,8 +9426,8 @@
     <s v="Dip Net"/>
     <s v="Scales"/>
     <n v="2"/>
-    <x v="2"/>
-    <x v="0"/>
+    <s v="11"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="3"/>
@@ -9434,8 +9447,8 @@
     <s v="Gaff"/>
     <s v="Scales"/>
     <n v="1"/>
-    <x v="2"/>
-    <x v="0"/>
+    <s v="11"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="3"/>
@@ -9455,8 +9468,8 @@
     <s v="Gaff"/>
     <s v="Scales"/>
     <n v="2"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorbed Age Interpretation. Resorption affecting age and missing 1 marine annulus"/>
     <x v="0"/>
@@ -9476,8 +9489,8 @@
     <s v="Dip Net"/>
     <s v="Otoliths and Scales"/>
     <n v="1"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorbed Age Interpretation. Resorption affecting age and missing 1 marine annulus"/>
     <x v="0"/>
@@ -9497,8 +9510,8 @@
     <s v="Dip Net"/>
     <s v="Otoliths and Scales"/>
     <n v="2"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -9518,8 +9531,8 @@
     <s v="Dip Net"/>
     <s v="Otoliths and Scales"/>
     <n v="3"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorbed Age Interpretation. Resorption affecting age and missing 1 marine annulus"/>
     <x v="0"/>
@@ -9539,8 +9552,8 @@
     <s v="Dip Net"/>
     <s v="Otoliths and Scales"/>
     <n v="4"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorbed Age Interpretation. Resorption affecting age and missing 1 marine annulus"/>
     <x v="0"/>
@@ -9560,8 +9573,8 @@
     <s v="Dip Net"/>
     <s v="Otoliths and Scales"/>
     <n v="5"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -9581,8 +9594,8 @@
     <s v="Dip Net"/>
     <s v="Otoliths and Scales"/>
     <n v="6"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorbed Age Interpretation. Resorption affecting age and missing 1 marine annulus"/>
     <x v="0"/>
@@ -9602,8 +9615,8 @@
     <s v="Dip Net"/>
     <s v="Otoliths and Scales"/>
     <n v="7"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorbed Age Interpretation. Resorption affecting age and missing 1 marine annulus"/>
     <x v="0"/>
@@ -9623,8 +9636,8 @@
     <s v="Dip Net"/>
     <s v="Otoliths and Scales"/>
     <n v="8"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorbed Age Interpretation. Resorption affecting age and missing 1 marine annulus"/>
     <x v="0"/>
@@ -9644,8 +9657,8 @@
     <s v="Dip Net"/>
     <s v="Otoliths and Scales"/>
     <n v="9"/>
-    <x v="3"/>
-    <x v="0"/>
+    <s v="02"/>
+    <m/>
     <m/>
     <s v="Resorbed Age Interpretation. Resorption affecting age and missing 1 marine annulus"/>
     <x v="4"/>
@@ -9665,8 +9678,8 @@
     <s v="Dip Net"/>
     <s v="Otoliths and Scales"/>
     <n v="10"/>
-    <x v="5"/>
-    <x v="0"/>
+    <s v="03"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="7"/>
@@ -9686,8 +9699,8 @@
     <s v="Dip Net"/>
     <s v="Otoliths and Scales"/>
     <n v="1"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorbed Age Interpretation. Resorption affecting age and missing 1 marine annulus"/>
     <x v="0"/>
@@ -9707,8 +9720,8 @@
     <s v="Dip Net"/>
     <s v="Otoliths and Scales"/>
     <n v="2"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorbed Age Interpretation. Resorption affecting age and missing 1 marine annulus"/>
     <x v="0"/>
@@ -9728,8 +9741,8 @@
     <s v="Dip Net"/>
     <s v="Otoliths and Scales"/>
     <n v="3"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorbed Age Interpretation. Resorption affecting age and missing 1 marine annulus"/>
     <x v="0"/>
@@ -9749,8 +9762,8 @@
     <s v="Dip Net"/>
     <s v="Otoliths and Scales"/>
     <n v="4"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorbed Age Interpretation. Resorption affecting age and missing 1 marine annulus"/>
     <x v="0"/>
@@ -9770,8 +9783,8 @@
     <s v="Dip Net"/>
     <s v="Otoliths and Scales"/>
     <n v="5"/>
-    <x v="1"/>
-    <x v="0"/>
+    <m/>
+    <m/>
     <s v="Wet Scale"/>
     <m/>
     <x v="1"/>
@@ -9791,8 +9804,8 @@
     <s v="Dip Net"/>
     <s v="Otoliths and Scales"/>
     <n v="6"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorbed Age Interpretation. Resorption affecting age and missing 1 marine annulus"/>
     <x v="0"/>
@@ -9812,8 +9825,8 @@
     <s v="Dip Net"/>
     <s v="Otoliths and Scales"/>
     <n v="7"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorbed Age Interpretation. Resorption affecting age and missing 1 marine annulus"/>
     <x v="0"/>
@@ -9833,8 +9846,8 @@
     <s v="Dip Net"/>
     <s v="Otoliths and Scales"/>
     <n v="1"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -9854,8 +9867,8 @@
     <s v="Dip Net"/>
     <s v="Otoliths and Scales"/>
     <n v="2"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="12"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="0"/>
@@ -9875,8 +9888,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="1"/>
-    <x v="3"/>
-    <x v="0"/>
+    <s v="02"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="4"/>
@@ -9896,8 +9909,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="2"/>
-    <x v="5"/>
-    <x v="0"/>
+    <s v="03"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="7"/>
@@ -9917,8 +9930,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="3"/>
-    <x v="1"/>
-    <x v="1"/>
+    <m/>
+    <s v="M2"/>
     <s v="Regenerate Scale"/>
     <s v="Resorbed Age Interpretation. Resorption affecting age and missing 1 marine annulus"/>
     <x v="2"/>
@@ -9938,8 +9951,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="1"/>
-    <x v="3"/>
-    <x v="0"/>
+    <s v="02"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="4"/>
@@ -9959,8 +9972,8 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="2"/>
-    <x v="5"/>
-    <x v="0"/>
+    <s v="03"/>
+    <m/>
     <m/>
     <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="7"/>
@@ -9980,29 +9993,932 @@
     <s v="Gaff"/>
     <s v="Otoliths and Scales"/>
     <n v="3"/>
-    <x v="1"/>
-    <x v="1"/>
+    <m/>
+    <s v="M2"/>
     <s v="Regenerate Scale"/>
     <s v="Resorbed Age Interpretation. Resorption affecting age and missing 1 marine annulus"/>
     <x v="2"/>
   </r>
   <r>
-    <m/>
+    <n v="141539"/>
     <x v="3"/>
+    <x v="0"/>
+    <s v="8"/>
+    <x v="1"/>
+    <s v="1080831"/>
+    <s v="2025-07-07"/>
+    <s v="2025-07-27"/>
+    <x v="0"/>
+    <s v="Adult"/>
+    <s v="First Nations - FSC"/>
+    <s v="Gillnet"/>
+    <s v="Scales"/>
+    <n v="1"/>
+    <s v="13"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="5"/>
+  </r>
+  <r>
+    <n v="141539"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="8"/>
+    <x v="1"/>
+    <s v="1080831"/>
+    <s v="2025-07-07"/>
+    <s v="2025-07-27"/>
+    <x v="0"/>
+    <s v="Adult"/>
+    <s v="First Nations - FSC"/>
+    <s v="Gillnet"/>
+    <s v="Scales"/>
+    <n v="2"/>
+    <s v="12"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="141539"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="8"/>
+    <x v="1"/>
+    <s v="1080831"/>
+    <s v="2025-07-07"/>
+    <s v="2025-07-27"/>
+    <x v="0"/>
+    <s v="Adult"/>
+    <s v="First Nations - FSC"/>
+    <s v="Gillnet"/>
+    <s v="Scales"/>
+    <n v="3"/>
+    <s v="12"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="141539"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="8"/>
+    <x v="1"/>
+    <s v="1080831"/>
+    <s v="2025-07-07"/>
+    <s v="2025-07-27"/>
+    <x v="0"/>
+    <s v="Adult"/>
+    <s v="First Nations - FSC"/>
+    <s v="Gillnet"/>
+    <s v="Scales"/>
+    <n v="4"/>
+    <s v="12"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="141539"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="8"/>
+    <x v="1"/>
+    <s v="1080831"/>
+    <s v="2025-07-07"/>
+    <s v="2025-07-27"/>
+    <x v="0"/>
+    <s v="Adult"/>
+    <s v="First Nations - FSC"/>
+    <s v="Gillnet"/>
+    <s v="Scales"/>
+    <n v="5"/>
+    <s v="12"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="141539"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="8"/>
+    <x v="1"/>
+    <s v="1080831"/>
+    <s v="2025-07-07"/>
+    <s v="2025-07-27"/>
+    <x v="0"/>
+    <s v="Adult"/>
+    <s v="First Nations - FSC"/>
+    <s v="Gillnet"/>
+    <s v="Scales"/>
+    <n v="6"/>
+    <s v="13"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="5"/>
+  </r>
+  <r>
+    <n v="141539"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="8"/>
+    <x v="1"/>
+    <s v="1080831"/>
+    <s v="2025-07-07"/>
+    <s v="2025-07-27"/>
+    <x v="0"/>
+    <s v="Adult"/>
+    <s v="First Nations - FSC"/>
+    <s v="Gillnet"/>
+    <s v="Scales"/>
+    <n v="7"/>
+    <s v="13"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="5"/>
+  </r>
+  <r>
+    <n v="141539"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="8"/>
+    <x v="1"/>
+    <s v="1080831"/>
+    <s v="2025-07-07"/>
+    <s v="2025-07-27"/>
+    <x v="0"/>
+    <s v="Adult"/>
+    <s v="First Nations - FSC"/>
+    <s v="Gillnet"/>
+    <s v="Scales"/>
+    <n v="8"/>
+    <s v="12"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="141539"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="8"/>
+    <x v="1"/>
+    <s v="1080831"/>
+    <s v="2025-07-07"/>
+    <s v="2025-07-27"/>
+    <x v="0"/>
+    <s v="Adult"/>
+    <s v="First Nations - FSC"/>
+    <s v="Gillnet"/>
+    <s v="Scales"/>
+    <n v="9"/>
+    <s v="13"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="5"/>
+  </r>
+  <r>
+    <n v="141539"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="8"/>
+    <x v="1"/>
+    <s v="1080831"/>
+    <s v="2025-07-07"/>
+    <s v="2025-07-27"/>
+    <x v="0"/>
+    <s v="Adult"/>
+    <s v="First Nations - FSC"/>
+    <s v="Gillnet"/>
+    <s v="Scales"/>
+    <n v="10"/>
+    <s v="12"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="141539"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="8"/>
+    <x v="1"/>
+    <s v="1080831"/>
+    <s v="2025-07-07"/>
+    <s v="2025-07-27"/>
+    <x v="0"/>
+    <s v="Adult"/>
+    <s v="First Nations - FSC"/>
+    <s v="Gillnet"/>
+    <s v="Scales"/>
+    <n v="11"/>
+    <s v="03"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="7"/>
+  </r>
+  <r>
+    <n v="141539"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="8"/>
+    <x v="1"/>
+    <s v="1080831"/>
+    <s v="2025-07-07"/>
+    <s v="2025-07-27"/>
+    <x v="0"/>
+    <s v="Adult"/>
+    <s v="First Nations - FSC"/>
+    <s v="Gillnet"/>
+    <s v="Scales"/>
+    <n v="12"/>
+    <s v="02"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="141539"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="8"/>
+    <x v="1"/>
+    <s v="1080831"/>
+    <s v="2025-07-07"/>
+    <s v="2025-07-27"/>
+    <x v="0"/>
+    <s v="Adult"/>
+    <s v="First Nations - FSC"/>
+    <s v="Gillnet"/>
+    <s v="Scales"/>
+    <n v="13"/>
+    <s v="13"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="5"/>
+  </r>
+  <r>
+    <n v="141539"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="8"/>
+    <x v="1"/>
+    <s v="1080831"/>
+    <s v="2025-07-07"/>
+    <s v="2025-07-27"/>
+    <x v="0"/>
+    <s v="Adult"/>
+    <s v="First Nations - FSC"/>
+    <s v="Gillnet"/>
+    <s v="Scales"/>
+    <n v="14"/>
+    <s v="12"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="141539"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="8"/>
+    <x v="1"/>
+    <s v="1080831"/>
+    <s v="2025-07-07"/>
+    <s v="2025-07-27"/>
+    <x v="0"/>
+    <s v="Adult"/>
+    <s v="First Nations - FSC"/>
+    <s v="Gillnet"/>
+    <s v="Scales"/>
+    <n v="15"/>
+    <s v="12"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="141539"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="8"/>
+    <x v="1"/>
+    <s v="1080831"/>
+    <s v="2025-07-07"/>
+    <s v="2025-07-27"/>
+    <x v="0"/>
+    <s v="Adult"/>
+    <s v="First Nations - FSC"/>
+    <s v="Gillnet"/>
+    <s v="Scales"/>
+    <n v="16"/>
+    <s v="12"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="141539"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="8"/>
+    <x v="1"/>
+    <s v="1080831"/>
+    <s v="2025-07-07"/>
+    <s v="2025-07-27"/>
+    <x v="0"/>
+    <s v="Adult"/>
+    <s v="First Nations - FSC"/>
+    <s v="Gillnet"/>
+    <s v="Scales"/>
+    <n v="17"/>
+    <m/>
+    <s v="M2"/>
+    <s v="Regenerate Scale"/>
+    <m/>
     <x v="2"/>
-    <m/>
+  </r>
+  <r>
+    <n v="141539"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="8"/>
+    <x v="1"/>
+    <s v="1080831"/>
+    <s v="2025-07-07"/>
+    <s v="2025-07-27"/>
+    <x v="0"/>
+    <s v="Adult"/>
+    <s v="First Nations - FSC"/>
+    <s v="Gillnet"/>
+    <s v="Scales"/>
+    <n v="18"/>
+    <s v="03"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="7"/>
+  </r>
+  <r>
+    <n v="141539"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="8"/>
+    <x v="1"/>
+    <s v="1080831"/>
+    <s v="2025-07-07"/>
+    <s v="2025-07-27"/>
+    <x v="0"/>
+    <s v="Adult"/>
+    <s v="First Nations - FSC"/>
+    <s v="Gillnet"/>
+    <s v="Scales"/>
+    <n v="19"/>
+    <m/>
+    <m/>
+    <s v="Regenerate Scale"/>
+    <m/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="141539"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="8"/>
+    <x v="1"/>
+    <s v="1080831"/>
+    <s v="2025-07-07"/>
+    <s v="2025-07-27"/>
+    <x v="0"/>
+    <s v="Adult"/>
+    <s v="First Nations - FSC"/>
+    <s v="Gillnet"/>
+    <s v="Scales"/>
+    <n v="20"/>
+    <s v="12"/>
+    <m/>
+    <m/>
+    <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="141539"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="8"/>
+    <x v="1"/>
+    <s v="1080831"/>
+    <s v="2025-07-07"/>
+    <s v="2025-07-27"/>
+    <x v="0"/>
+    <s v="Adult"/>
+    <s v="First Nations - FSC"/>
+    <s v="Gillnet"/>
+    <s v="Scales"/>
+    <n v="21"/>
+    <s v="12"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="141539"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="8"/>
+    <x v="1"/>
+    <s v="1080831"/>
+    <s v="2025-07-07"/>
+    <s v="2025-07-27"/>
+    <x v="0"/>
+    <s v="Adult"/>
+    <s v="First Nations - FSC"/>
+    <s v="Gillnet"/>
+    <s v="Scales"/>
+    <n v="22"/>
+    <m/>
+    <s v="M2"/>
+    <s v="Regenerate Scale"/>
+    <m/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="141539"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="8"/>
+    <x v="1"/>
+    <s v="1080831"/>
+    <s v="2025-07-07"/>
+    <s v="2025-07-27"/>
+    <x v="0"/>
+    <s v="Adult"/>
+    <s v="First Nations - FSC"/>
+    <s v="Gillnet"/>
+    <s v="Scales"/>
+    <n v="23"/>
+    <s v="03"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="7"/>
+  </r>
+  <r>
+    <n v="141539"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="8"/>
+    <x v="1"/>
+    <s v="1080831"/>
+    <s v="2025-07-07"/>
+    <s v="2025-07-27"/>
+    <x v="0"/>
+    <s v="Adult"/>
+    <s v="First Nations - FSC"/>
+    <s v="Gillnet"/>
+    <s v="Scales"/>
+    <n v="24"/>
+    <s v="12"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="141539"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="8"/>
+    <x v="1"/>
+    <s v="1080831"/>
+    <s v="2025-07-07"/>
+    <s v="2025-07-27"/>
+    <x v="0"/>
+    <s v="Adult"/>
+    <s v="First Nations - FSC"/>
+    <s v="Gillnet"/>
+    <s v="Scales"/>
+    <n v="25"/>
+    <m/>
+    <s v="M2"/>
+    <s v="Regenerate Scale"/>
+    <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="141539"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="8"/>
+    <x v="1"/>
+    <s v="1080832"/>
+    <s v="2025-07-21"/>
+    <s v="2025-07-27"/>
+    <x v="0"/>
+    <s v="Adult"/>
+    <s v="First Nations - FSC"/>
+    <s v="Gillnet"/>
+    <s v="Scales"/>
+    <n v="1"/>
+    <s v="12"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="141539"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="8"/>
+    <x v="1"/>
+    <s v="1080832"/>
+    <s v="2025-07-21"/>
+    <s v="2025-07-27"/>
+    <x v="0"/>
+    <s v="Adult"/>
+    <s v="First Nations - FSC"/>
+    <s v="Gillnet"/>
+    <s v="Scales"/>
+    <n v="2"/>
+    <s v="13"/>
+    <m/>
+    <m/>
+    <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
+    <x v="5"/>
+  </r>
+  <r>
+    <n v="141539"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="8"/>
+    <x v="1"/>
+    <s v="1080832"/>
+    <s v="2025-07-21"/>
+    <s v="2025-07-27"/>
+    <x v="0"/>
+    <s v="Adult"/>
+    <s v="First Nations - FSC"/>
+    <s v="Gillnet"/>
+    <s v="Scales"/>
+    <n v="3"/>
+    <s v="02"/>
+    <m/>
+    <m/>
+    <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="141539"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="8"/>
+    <x v="1"/>
+    <s v="1080832"/>
+    <s v="2025-07-21"/>
+    <s v="2025-07-27"/>
+    <x v="0"/>
+    <s v="Adult"/>
+    <s v="First Nations - FSC"/>
+    <s v="Gillnet"/>
+    <s v="Scales"/>
+    <n v="4"/>
+    <s v="13"/>
+    <m/>
+    <m/>
+    <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
+    <x v="5"/>
+  </r>
+  <r>
+    <n v="141539"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="8"/>
+    <x v="1"/>
+    <s v="1080832"/>
+    <s v="2025-07-21"/>
+    <s v="2025-07-27"/>
+    <x v="0"/>
+    <s v="Adult"/>
+    <s v="First Nations - FSC"/>
+    <s v="Gillnet"/>
+    <s v="Scales"/>
+    <n v="5"/>
+    <s v="12"/>
+    <m/>
+    <m/>
+    <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="141539"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="8"/>
+    <x v="1"/>
+    <s v="1080832"/>
+    <s v="2025-07-21"/>
+    <s v="2025-07-27"/>
+    <x v="0"/>
+    <s v="Adult"/>
+    <s v="First Nations - FSC"/>
+    <s v="Gillnet"/>
+    <s v="Scales"/>
+    <n v="6"/>
+    <s v="13"/>
+    <m/>
+    <m/>
+    <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
+    <x v="5"/>
+  </r>
+  <r>
+    <n v="141539"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="8"/>
+    <x v="1"/>
+    <s v="1080832"/>
+    <s v="2025-07-21"/>
+    <s v="2025-07-27"/>
+    <x v="0"/>
+    <s v="Adult"/>
+    <s v="First Nations - FSC"/>
+    <s v="Gillnet"/>
+    <s v="Scales"/>
+    <n v="7"/>
+    <s v="12"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="141539"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="8"/>
+    <x v="1"/>
+    <s v="1080832"/>
+    <s v="2025-07-21"/>
+    <s v="2025-07-27"/>
+    <x v="0"/>
+    <s v="Adult"/>
+    <s v="First Nations - FSC"/>
+    <s v="Gillnet"/>
+    <s v="Scales"/>
+    <n v="8"/>
+    <s v="12"/>
+    <m/>
+    <m/>
+    <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="141539"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="8"/>
+    <x v="1"/>
+    <s v="1080832"/>
+    <s v="2025-07-21"/>
+    <s v="2025-07-27"/>
+    <x v="0"/>
+    <s v="Adult"/>
+    <s v="First Nations - FSC"/>
+    <s v="Gillnet"/>
+    <s v="Scales"/>
+    <n v="9"/>
+    <s v="22"/>
+    <m/>
+    <m/>
+    <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="9"/>
-    <m/>
-    <m/>
-    <m/>
+  </r>
+  <r>
+    <n v="141539"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="8"/>
+    <x v="1"/>
+    <s v="1080832"/>
+    <s v="2025-07-21"/>
+    <s v="2025-07-27"/>
+    <x v="0"/>
+    <s v="Adult"/>
+    <s v="First Nations - FSC"/>
+    <s v="Gillnet"/>
+    <s v="Scales"/>
+    <n v="10"/>
+    <s v="22"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="9"/>
+  </r>
+  <r>
+    <n v="141539"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="8"/>
+    <x v="1"/>
+    <s v="1080832"/>
+    <s v="2025-07-21"/>
+    <s v="2025-07-27"/>
+    <x v="0"/>
+    <s v="Adult"/>
+    <s v="First Nations - FSC"/>
+    <s v="Gillnet"/>
+    <s v="Scales"/>
+    <n v="11"/>
+    <m/>
+    <s v="M2"/>
+    <s v="Regenerate Scale"/>
+    <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
     <x v="2"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <x v="1"/>
-    <x v="0"/>
+  </r>
+  <r>
+    <n v="141539"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="8"/>
+    <x v="1"/>
+    <s v="1080832"/>
+    <s v="2025-07-21"/>
+    <s v="2025-07-27"/>
+    <x v="0"/>
+    <s v="Adult"/>
+    <s v="First Nations - FSC"/>
+    <s v="Gillnet"/>
+    <s v="Scales"/>
+    <n v="12"/>
+    <m/>
+    <m/>
+    <s v="No Structure"/>
+    <m/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="141539"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="8"/>
+    <x v="1"/>
+    <s v="1080832"/>
+    <s v="2025-07-21"/>
+    <s v="2025-07-27"/>
+    <x v="0"/>
+    <s v="Adult"/>
+    <s v="First Nations - FSC"/>
+    <s v="Gillnet"/>
+    <s v="Scales"/>
+    <n v="13"/>
+    <m/>
+    <m/>
+    <s v="No Structure"/>
+    <m/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="141539"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="8"/>
+    <x v="1"/>
+    <s v="1080832"/>
+    <s v="2025-07-21"/>
+    <s v="2025-07-27"/>
+    <x v="0"/>
+    <s v="Adult"/>
+    <s v="First Nations - FSC"/>
+    <s v="Gillnet"/>
+    <s v="Scales"/>
+    <n v="14"/>
+    <m/>
+    <s v="M2"/>
+    <s v="Regenerate Scale"/>
+    <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="141539"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="8"/>
+    <x v="1"/>
+    <s v="1080832"/>
+    <s v="2025-07-21"/>
+    <s v="2025-07-27"/>
+    <x v="0"/>
+    <s v="Adult"/>
+    <s v="First Nations - FSC"/>
+    <s v="Gillnet"/>
+    <s v="Scales"/>
+    <n v="15"/>
+    <s v="13"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="5"/>
+  </r>
+  <r>
+    <n v="141539"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="8"/>
+    <x v="1"/>
+    <s v="1080832"/>
+    <s v="2025-07-21"/>
+    <s v="2025-07-27"/>
+    <x v="0"/>
+    <s v="Adult"/>
+    <s v="First Nations - FSC"/>
+    <s v="Gillnet"/>
+    <s v="Scales"/>
+    <n v="16"/>
+    <s v="13"/>
+    <m/>
+    <m/>
+    <s v="Resorption present but not enough to suspect an annuli is missing.  Age unaffected."/>
+    <x v="5"/>
+  </r>
+  <r>
+    <n v="141539"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="8"/>
+    <x v="1"/>
+    <s v="1080832"/>
+    <s v="2025-07-21"/>
+    <s v="2025-07-27"/>
+    <x v="0"/>
+    <s v="Adult"/>
+    <s v="First Nations - FSC"/>
+    <s v="Gillnet"/>
+    <s v="Scales"/>
+    <n v="17"/>
+    <s v="12"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="141539"/>
+    <x v="3"/>
+    <x v="0"/>
+    <s v="8"/>
+    <x v="1"/>
+    <s v="1080832"/>
+    <s v="2025-07-21"/>
+    <s v="2025-07-27"/>
+    <x v="1"/>
+    <s v="Adult"/>
+    <s v="First Nations - FSC"/>
+    <s v="Gillnet"/>
+    <s v="Scales"/>
+    <n v="18"/>
+    <m/>
+    <s v="M1"/>
+    <s v="Regenerate Scale"/>
+    <m/>
+    <x v="12"/>
+  </r>
+  <r>
+    <m/>
+    <x v="4"/>
+    <x v="2"/>
+    <m/>
+    <x v="9"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="2"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
     <m/>
     <m/>
     <x v="1"/>
@@ -10011,15 +10927,16 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8C7D7B65-33F4-4604-B12A-06B567079BED}" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:N27" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8C7D7B65-33F4-4604-B12A-06B567079BED}" name="PivotTable3" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:N29" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="19">
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
-      <items count="5">
+      <items count="6">
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
+        <item x="4"/>
         <item x="3"/>
         <item t="default"/>
       </items>
@@ -10064,33 +10981,12 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="9">
-        <item x="3"/>
-        <item x="5"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="4"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisCol" dataField="1" showAll="0">
-      <items count="13">
+      <items count="14">
         <item x="11"/>
         <item x="8"/>
         <item x="2"/>
@@ -10103,6 +10999,7 @@
         <item x="9"/>
         <item x="10"/>
         <item x="1"/>
+        <item x="12"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -10112,7 +11009,7 @@
     <field x="1"/>
     <field x="4"/>
   </rowFields>
-  <rowItems count="23">
+  <rowItems count="25">
     <i>
       <x/>
     </i>
@@ -10179,6 +11076,12 @@
     <i r="2">
       <x v="3"/>
     </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="2">
+      <x v="3"/>
+    </i>
     <i t="grand">
       <x/>
     </i>
@@ -10229,6 +11132,142 @@
   </colItems>
   <pageFields count="1">
     <pageField fld="8" item="1" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Count of GR AGE" fld="18" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{90D5FD19-A247-4496-84C2-18BC66AEC2A2}" name="PivotTable2" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A4:H10" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="19">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="11">
+        <item h="1" x="7"/>
+        <item h="1" x="2"/>
+        <item h="1" x="5"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item h="1" x="3"/>
+        <item h="1" x="6"/>
+        <item h="1" x="8"/>
+        <item h="1" x="4"/>
+        <item h="1" x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" dataField="1" showAll="0">
+      <items count="14">
+        <item h="1" x="11"/>
+        <item h="1" x="8"/>
+        <item h="1" x="12"/>
+        <item h="1" x="2"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item h="1" x="6"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item h="1" x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="18"/>
+  </colFields>
+  <colItems count="7">
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="2" item="1" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
   </pageFields>
   <dataFields count="1">
     <dataField name="Count of GR AGE" fld="18" subtotal="count" baseField="0" baseItem="0"/>
@@ -13340,20 +14379,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CCAB895-930E-4093-B0AF-3713AC11B200}">
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:N29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="2.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="3.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="2.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="2.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="3.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="2.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="7.5703125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="2.85546875" bestFit="1" customWidth="1"/>
@@ -13788,25 +14827,28 @@
         <v>24</v>
       </c>
       <c r="D20">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G20">
         <v>5</v>
       </c>
       <c r="H20">
+        <v>5</v>
+      </c>
+      <c r="I20">
+        <v>37</v>
+      </c>
+      <c r="J20">
+        <v>14</v>
+      </c>
+      <c r="K20">
         <v>2</v>
       </c>
-      <c r="I20">
-        <v>20</v>
-      </c>
-      <c r="J20">
-        <v>4</v>
-      </c>
       <c r="N20">
-        <v>37</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
@@ -13936,44 +14978,96 @@
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="10" t="s">
+      <c r="A27" s="11">
+        <v>2025</v>
+      </c>
+      <c r="D27">
+        <v>5</v>
+      </c>
+      <c r="E27">
+        <v>2</v>
+      </c>
+      <c r="H27">
+        <v>3</v>
+      </c>
+      <c r="I27">
+        <v>17</v>
+      </c>
+      <c r="J27">
+        <v>10</v>
+      </c>
+      <c r="K27">
+        <v>2</v>
+      </c>
+      <c r="N27">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="D28">
+        <v>5</v>
+      </c>
+      <c r="E28">
+        <v>2</v>
+      </c>
+      <c r="H28">
+        <v>3</v>
+      </c>
+      <c r="I28">
+        <v>17</v>
+      </c>
+      <c r="J28">
+        <v>10</v>
+      </c>
+      <c r="K28">
+        <v>2</v>
+      </c>
+      <c r="N28">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="10" t="s">
         <v>337</v>
       </c>
-      <c r="B27">
+      <c r="B29">
         <v>3</v>
       </c>
-      <c r="C27">
-        <v>32</v>
-      </c>
-      <c r="D27">
+      <c r="C29">
+        <v>32</v>
+      </c>
+      <c r="D29">
+        <v>15</v>
+      </c>
+      <c r="E29">
         <v>10</v>
       </c>
-      <c r="E27">
-        <v>8</v>
-      </c>
-      <c r="F27">
+      <c r="F29">
         <v>6</v>
       </c>
-      <c r="G27">
+      <c r="G29">
         <v>6</v>
       </c>
-      <c r="H27">
-        <v>13</v>
-      </c>
-      <c r="I27">
-        <v>221</v>
-      </c>
-      <c r="J27">
-        <v>69</v>
-      </c>
-      <c r="K27">
-        <v>3</v>
-      </c>
-      <c r="L27">
+      <c r="H29">
+        <v>16</v>
+      </c>
+      <c r="I29">
+        <v>238</v>
+      </c>
+      <c r="J29">
+        <v>79</v>
+      </c>
+      <c r="K29">
+        <v>5</v>
+      </c>
+      <c r="L29">
         <v>2</v>
       </c>
-      <c r="N27">
-        <v>373</v>
+      <c r="N29">
+        <v>412</v>
       </c>
     </row>
   </sheetData>
@@ -13982,6 +15076,296 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7701AC7-0439-4F5B-9235-8C6F328FBEB5}">
+  <dimension ref="A1:T10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="B5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" t="s">
+        <v>198</v>
+      </c>
+      <c r="E5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F5" t="s">
+        <v>69</v>
+      </c>
+      <c r="G5" t="s">
+        <v>276</v>
+      </c>
+      <c r="H5" t="s">
+        <v>337</v>
+      </c>
+      <c r="O5">
+        <v>2</v>
+      </c>
+      <c r="P5">
+        <v>3</v>
+      </c>
+      <c r="Q5">
+        <v>4</v>
+      </c>
+      <c r="R5">
+        <v>5</v>
+      </c>
+      <c r="S5">
+        <v>6</v>
+      </c>
+      <c r="T5" s="13" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A6" s="10">
+        <v>2022</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>8</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>13</v>
+      </c>
+      <c r="N6" s="10">
+        <v>2022</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <f>SUM(B6:C6)</f>
+        <v>3</v>
+      </c>
+      <c r="Q6">
+        <f>SUM(D6:E6)</f>
+        <v>8</v>
+      </c>
+      <c r="R6">
+        <f>SUM(F6:G6)</f>
+        <v>2</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <f>SUM(O6:S6)</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A7" s="10">
+        <v>2023</v>
+      </c>
+      <c r="E7">
+        <v>6</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>7</v>
+      </c>
+      <c r="N7" s="10">
+        <v>2023</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <f t="shared" ref="P7:P9" si="0">SUM(B7:C7)</f>
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" ref="Q7:Q9" si="1">SUM(D7:E7)</f>
+        <v>6</v>
+      </c>
+      <c r="R7">
+        <f t="shared" ref="R7:R9" si="2">SUM(F7:G7)</f>
+        <v>1</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <f t="shared" ref="T7:T9" si="3">SUM(O7:S7)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A8" s="10">
+        <v>2024</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8">
+        <v>6</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>9</v>
+      </c>
+      <c r="N8" s="10">
+        <v>2024</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A9" s="10">
+        <v>2025</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="E9">
+        <v>17</v>
+      </c>
+      <c r="F9">
+        <v>10</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+      <c r="H9">
+        <v>34</v>
+      </c>
+      <c r="N9" s="10">
+        <v>2025</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="Q9">
+        <f>SUM(D9:E9)</f>
+        <v>20</v>
+      </c>
+      <c r="R9">
+        <f>SUM(F9:G9)</f>
+        <v>12</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="3"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10">
+        <v>5</v>
+      </c>
+      <c r="E10">
+        <v>37</v>
+      </c>
+      <c r="F10">
+        <v>14</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+      <c r="H10">
+        <v>63</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:S457"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -37427,7 +38811,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -38774,48 +40158,6 @@
       </c>
       <c r="F67" s="7" t="s">
         <v>81</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter>
-    <oddHeader>&amp;R&amp;"Calibri"&amp;12&amp;K000000 Unclassified - Non-Classifié&amp;1#_x000D_</oddHeader>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -38827,6 +40169,48 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;"Calibri"&amp;12&amp;K000000 Unclassified - Non-Classifié&amp;1#_x000D_</oddHeader>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:D49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
